--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487599_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487599_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6436</v>
+        <v>3.4537</v>
       </c>
       <c r="E2" t="n">
-        <v>4.395</v>
+        <v>1.1851</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2486</v>
+        <v>2.2686</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1955</v>
+        <v>1.8833</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3919</v>
+        <v>2.5095</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1963</v>
+        <v>-0.6262</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6065</v>
+        <v>0.8461</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5025</v>
+        <v>2.1174</v>
       </c>
       <c r="L2" t="n">
-        <v>0.104</v>
+        <v>-1.2712</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.411</v>
+        <v>1.0372</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1106</v>
+        <v>0.3921</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3004</v>
+        <v>0.645</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1642</v>
+        <v>1.9403</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3301</v>
+        <v>-0.0401</v>
       </c>
       <c r="T2" t="n">
-        <v>2.611</v>
+        <v>-0.2252</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2808</v>
+        <v>0.1851</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="W2" t="n">
-        <v>0.2821</v>
+        <v>0.5642</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3348</v>
+        <v>2.8596</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6846</v>
+        <v>2.393</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6502</v>
+        <v>0.4666</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8833</v>
+        <v>3.1955</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5095</v>
+        <v>3.3919</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6262</v>
+        <v>-0.1963</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8461</v>
+        <v>4.6065</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1174</v>
+        <v>4.5025</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2712</v>
+        <v>0.104</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0372</v>
+        <v>-1.411</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3921</v>
+        <v>-1.1106</v>
       </c>
       <c r="O3" t="n">
-        <v>0.645</v>
+        <v>-0.3004</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R3" t="n">
         <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.159</v>
+        <v>0.5462</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7257</v>
+        <v>0.609</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5667</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3299</v>
+        <v>0.2821</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5642</v>
+        <v>0.2821</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2572</v>
+        <v>1.4935</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1042</v>
+        <v>1.2043</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1529</v>
+        <v>0.2892</v>
       </c>
       <c r="G4" t="n">
         <v>0.499</v>
@@ -766,13 +766,13 @@
         <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0179</v>
+        <v>0.2184</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4834</v>
+        <v>-0.3833</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4655</v>
+        <v>0.6018</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1109</v>
+        <v>-0.0019</v>
       </c>
       <c r="E5" t="n">
         <v>0.9969</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1077</v>
+        <v>-0.9987</v>
       </c>
       <c r="G5" t="n">
         <v>-0.07480000000000001</v>
@@ -844,13 +844,13 @@
         <v>0.194</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2302</v>
+        <v>-0.1211</v>
       </c>
       <c r="T5" t="n">
         <v>-0.3028</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0727</v>
+        <v>0.1817</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DE LAS HERAS SANZ</t>
+          <t>J. BARRA DE LA CRUZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6914</v>
+        <v>-0.4953</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7466</v>
+        <v>-1.0982</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0552</v>
+        <v>0.6029</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.588</v>
+        <v>1.4672</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6286</v>
+        <v>2.9231</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0406</v>
+        <v>-1.4559</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5649</v>
+        <v>1.9818</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6055</v>
+        <v>3.2708</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0406</v>
+        <v>-1.289</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0231</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0231</v>
+        <v>-0.3477</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.1669</v>
       </c>
       <c r="P6" t="n">
-        <v>0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1045</v>
       </c>
       <c r="R6" t="n">
-        <v>0.194</v>
+        <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2974</v>
+        <v>-0.3729</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1817</v>
+        <v>-0.7739</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1157</v>
+        <v>0.401</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.4254</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.7985</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0859</v>
+        <v>-0.5131</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1273</v>
+        <v>-1.827</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0413</v>
+        <v>1.3139</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4807</v>
@@ -1000,13 +1000,13 @@
         <v>1.5523</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7514999999999999</v>
+        <v>-0.1786</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6046</v>
+        <v>-0.3043</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1469</v>
+        <v>0.1256</v>
       </c>
       <c r="V7" t="n">
         <v>0.5642</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BARRA DE LA CRUZ</t>
+          <t>A. DE LAS HERAS SANZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2689</v>
+        <v>-0.6186</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.899</v>
+        <v>-0.6465</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6301</v>
+        <v>0.028</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4672</v>
+        <v>-0.588</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9231</v>
+        <v>-0.6286</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4559</v>
+        <v>0.0406</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9818</v>
+        <v>-0.5649</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2708</v>
+        <v>-0.6055</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.289</v>
+        <v>0.0406</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.0231</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3477</v>
+        <v>-0.0231</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1669</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1045</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9403</v>
+        <v>0.194</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1465</v>
+        <v>-0.2246</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5747</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4283</v>
+        <v>-0.143</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.4254</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7985</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. DE LA CRUZ DE LA ROSA</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4578</v>
+        <v>-2.3134</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.157</v>
+        <v>-1.3895</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3008</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.1859</v>
+        <v>-0.2824</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7277</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4582</v>
+        <v>-0.2725</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6493</v>
+        <v>-0.3378</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2811</v>
+        <v>-0.3378</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6318</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5366</v>
+        <v>0.0554</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4466</v>
+        <v>0.3279</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.09</v>
+        <v>-0.2725</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>0.194</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3878</v>
+        <v>-0.1668</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1222</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2656</v>
+        <v>-0.0852</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6597</v>
+        <v>-0.894</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5642</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2239</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>L. DE LA CRUZ DE LA ROSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5225</v>
+        <v>-2.9216</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4896</v>
+        <v>-0.4573</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0329</v>
+        <v>-2.4643</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2824</v>
+        <v>-2.1859</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-1.7277</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2725</v>
+        <v>-0.4582</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3378</v>
+        <v>-0.6493</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3378</v>
+        <v>-1.2811</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.6318</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0554</v>
+        <v>-1.5366</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3279</v>
+        <v>-0.4466</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2725</v>
+        <v>-1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.376</v>
+        <v>-0.076</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1817</v>
+        <v>-0.1781</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1943</v>
+        <v>0.1021</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.894</v>
+        <v>-0.6597</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5642</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5138</v>
+        <v>-3.5678</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1836</v>
+        <v>-1.8833</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3302</v>
+        <v>-1.6845</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5458</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0902</v>
+        <v>0.0362</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0902</v>
+        <v>-0.7899</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1804</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-0.894</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9849</v>
+        <v>-3.7758</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.238</v>
+        <v>-2.1379</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7469</v>
+        <v>-1.6379</v>
       </c>
       <c r="G12" t="n">
         <v>0.7838000000000001</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4971</v>
+        <v>-0.288</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2412</v>
+        <v>-0.1411</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2559</v>
+        <v>-0.1469</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1075</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.400499999999999</v>
+        <v>-6.400700000000001</v>
       </c>
       <c r="E13" t="n">
         <v>-3.6604</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7402</v>
+        <v>-2.7401</v>
       </c>
       <c r="G13" t="n">
         <v>1.6712</v>
@@ -1447,7 +1447,7 @@
         <v>9.7301</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1671999999999997</v>
+        <v>0.1671999999999996</v>
       </c>
       <c r="M13" t="n">
         <v>-8.225800000000001</v>
@@ -1468,19 +1468,19 @@
         <v>11.6419</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6675</v>
+        <v>-0.6672999999999999</v>
       </c>
       <c r="T13" t="n">
         <v>-2.6528</v>
       </c>
       <c r="U13" t="n">
-        <v>1.9856</v>
+        <v>1.9855</v>
       </c>
       <c r="V13" t="n">
         <v>-5.4642</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6777</v>
+        <v>2.677700000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-8.1417</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4616</v>
+        <v>5.9427</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8401</v>
+        <v>3.8391</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6214</v>
+        <v>2.1036</v>
       </c>
       <c r="G14" t="n">
         <v>3.7094</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1402</v>
+        <v>0.6214</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7301</v>
+        <v>-0.2709</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4101</v>
+        <v>0.8922</v>
       </c>
       <c r="V14" t="n">
         <v>1.2239</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.102</v>
+        <v>4.7204</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5345</v>
+        <v>3.9348</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5675</v>
+        <v>0.7856</v>
       </c>
       <c r="G16" t="n">
         <v>2.6774</v>
@@ -1702,13 +1702,13 @@
         <v>1.7463</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9336</v>
+        <v>-0.3152</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1508</v>
+        <v>-0.7504</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2172</v>
+        <v>0.4352</v>
       </c>
       <c r="V16" t="n">
         <v>0.6119</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8754</v>
+        <v>2.366</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9063</v>
+        <v>1.5059</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9691</v>
+        <v>0.86</v>
       </c>
       <c r="G17" t="n">
         <v>1.4</v>
@@ -1780,13 +1780,13 @@
         <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0679</v>
+        <v>0.5585</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7301</v>
+        <v>0.3297</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3378</v>
+        <v>0.2288</v>
       </c>
       <c r="V17" t="n">
         <v>0.9896</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3631</v>
+        <v>1.0172</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6099</v>
+        <v>0.2095</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7532</v>
+        <v>0.8077</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0561</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6431</v>
+        <v>0.2972</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3039</v>
+        <v>-0.0965</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3392</v>
+        <v>0.3937</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2725</v>
+        <v>-0.0544</v>
       </c>
       <c r="E19" t="n">
         <v>-1.7292</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4567</v>
+        <v>1.6747</v>
       </c>
       <c r="G19" t="n">
         <v>-1.3624</v>
@@ -1936,13 +1936,13 @@
         <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7519</v>
+        <v>-0.5339</v>
       </c>
       <c r="T19" t="n">
         <v>-0.9691</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2172</v>
+        <v>0.4352</v>
       </c>
       <c r="V19" t="n">
         <v>0.0955</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3571</v>
+        <v>-0.7842</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3298</v>
+        <v>-1.0295</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0273</v>
+        <v>0.2453</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1447</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6303</v>
+        <v>-0.0575</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1806</v>
+        <v>0.1197</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4497</v>
+        <v>-0.1772</v>
       </c>
       <c r="V20" t="n">
         <v>1.2239</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0587</v>
+        <v>-1.5587</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3156</v>
+        <v>-2.1154</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2569</v>
+        <v>0.5567</v>
       </c>
       <c r="G21" t="n">
         <v>-1.9804</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8544</v>
+        <v>-0.3544</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.12</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.4346</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3949</v>
+        <v>-1.7849</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8792</v>
+        <v>-0.0784</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5157</v>
+        <v>-1.7065</v>
       </c>
       <c r="G22" t="n">
         <v>-1.312</v>
@@ -2170,13 +2170,13 @@
         <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5769</v>
+        <v>0.0331</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7268</v>
+        <v>0.074</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1499</v>
+        <v>-0.0409</v>
       </c>
       <c r="V22" t="n">
         <v>-0.894</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8046</v>
+        <v>-3.7679</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8226</v>
+        <v>-3.6224</v>
       </c>
       <c r="F23" t="n">
-        <v>0.018</v>
+        <v>-0.1455</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6534</v>
@@ -2248,13 +2248,13 @@
         <v>1.3582</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0727</v>
+        <v>0.1093</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3623</v>
+        <v>-0.1621</v>
       </c>
       <c r="U23" t="n">
-        <v>0.435</v>
+        <v>0.2714</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6119</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8432</v>
+        <v>-5.0251</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1304</v>
+        <v>-4.2305</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7128</v>
+        <v>-0.7946</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3461</v>
@@ -2326,13 +2326,13 @@
         <v>0.5821</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1149</v>
+        <v>-0.067</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0617</v>
+        <v>-0.0384</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0532</v>
+        <v>-0.0286</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2239</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.4006</v>
+        <v>6.400600000000003</v>
       </c>
       <c r="E25" t="n">
-        <v>1.516300000000001</v>
+        <v>1.5162</v>
       </c>
       <c r="F25" t="n">
-        <v>4.8841</v>
+        <v>4.884099999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-1.671199999999998</v>
@@ -2404,13 +2404,13 @@
         <v>13.5822</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6674000000000002</v>
+        <v>0.6671999999999998</v>
       </c>
       <c r="T25" t="n">
         <v>-1.9855</v>
       </c>
       <c r="U25" t="n">
-        <v>2.653</v>
+        <v>2.652699999999999</v>
       </c>
       <c r="V25" t="n">
         <v>5.464199999999998</v>
